--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486473_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486473_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.0399</v>
+        <v>7.1401</v>
       </c>
       <c r="E2" t="n">
-        <v>7.3229</v>
+        <v>7.5464</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.283</v>
+        <v>-0.4063</v>
       </c>
       <c r="G2" t="n">
         <v>5.6813</v>
@@ -610,13 +610,13 @@
         <v>0.87</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.7262999999999999</v>
+        <v>-0.6261</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.4795</v>
+        <v>-0.256</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2468</v>
+        <v>-0.3701</v>
       </c>
       <c r="V2" t="n">
         <v>3.3899</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3794</v>
+        <v>0.2561</v>
       </c>
       <c r="E3" t="n">
         <v>0.0125</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3669</v>
+        <v>0.2436</v>
       </c>
       <c r="G3" t="n">
         <v>-0.5334</v>
@@ -688,13 +688,13 @@
         <v>1.0875</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1747</v>
+        <v>-0.298</v>
       </c>
       <c r="T3" t="n">
         <v>-0.137</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0377</v>
+        <v>-0.161</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. GARCIA SANCHEZ</t>
+          <t>N. HOOVER</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3567</v>
+        <v>0.1816</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6161</v>
+        <v>-0.545</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.2593</v>
+        <v>0.7266</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.07489999999999999</v>
+        <v>1.6089</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.067</v>
+        <v>0.5077</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.008</v>
+        <v>1.1013</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0765</v>
+        <v>1.9215</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>1.0585</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0765</v>
+        <v>0.863</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.1514</v>
+        <v>-0.3126</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.067</v>
+        <v>-0.5508</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.08450000000000001</v>
+        <v>0.2382</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>-0.6525</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-2.1751</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.5225</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4317</v>
+        <v>-0.9493</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5396</v>
+        <v>-0.4867</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1079</v>
+        <v>-0.4627</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.1745</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.0207</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. CAICEDO SANCHEZ</t>
+          <t>J. GARCIA SANCHEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.395</v>
+        <v>-0.0287</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5683</v>
+        <v>0.169</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.9633</v>
+        <v>-0.1977</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9425</v>
+        <v>-0.07489999999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>2.0135</v>
+        <v>-0.067</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.071</v>
+        <v>-0.008</v>
       </c>
       <c r="J5" t="n">
-        <v>2.899</v>
+        <v>0.0765</v>
       </c>
       <c r="K5" t="n">
-        <v>3.1452</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.2462</v>
+        <v>0.0765</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.9565</v>
+        <v>-0.1514</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.1318</v>
+        <v>-0.067</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.8248</v>
+        <v>-0.08450000000000001</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.87</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.305</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4673</v>
+        <v>0.0463</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3509</v>
+        <v>0.0925</v>
       </c>
       <c r="U5" t="n">
-        <v>0.8182</v>
+        <v>-0.0463</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.9347</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>N. HOOVER</t>
+          <t>J. GODSPOWER JOHNSON</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.5236</v>
+        <v>-0.4736</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.8803</v>
+        <v>0.6935</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3567</v>
+        <v>-1.1671</v>
       </c>
       <c r="G6" t="n">
-        <v>1.6089</v>
+        <v>-0.3669</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5077</v>
+        <v>0.6659</v>
       </c>
       <c r="I6" t="n">
-        <v>1.1013</v>
+        <v>-1.0327</v>
       </c>
       <c r="J6" t="n">
-        <v>1.9215</v>
+        <v>1.6717</v>
       </c>
       <c r="K6" t="n">
-        <v>1.0585</v>
+        <v>1.8797</v>
       </c>
       <c r="L6" t="n">
-        <v>0.863</v>
+        <v>-0.2079</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.3126</v>
+        <v>-2.0386</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.5508</v>
+        <v>-1.2138</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2382</v>
+        <v>-0.8248</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.6525</v>
+        <v>0.2175</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.1751</v>
+        <v>-1.0875</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5225</v>
+        <v>1.305</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.6545</v>
+        <v>-0.7147</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.822</v>
+        <v>-0.2812</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.8325</v>
+        <v>-0.4335</v>
       </c>
       <c r="V6" t="n">
-        <v>0.1745</v>
+        <v>0.3904</v>
       </c>
       <c r="W6" t="n">
-        <v>0.1952</v>
+        <v>0.3904</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.0207</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.8946</v>
+        <v>-0.8809</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1384</v>
+        <v>0.2753</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.033</v>
+        <v>-1.1562</v>
       </c>
       <c r="G7" t="n">
         <v>0.1791</v>
@@ -1000,13 +1000,13 @@
         <v>1.5225</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5533</v>
+        <v>-0.5396</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.7534999999999999</v>
+        <v>-0.6165</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2002</v>
+        <v>0.0769</v>
       </c>
       <c r="V7" t="n">
         <v>-0.9554</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.0711</v>
+        <v>-0.9101</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.1883</v>
+        <v>-1.1198</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1172</v>
+        <v>0.2097</v>
       </c>
       <c r="G8" t="n">
         <v>-0.9893</v>
@@ -1078,13 +1078,13 @@
         <v>0.87</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2123</v>
+        <v>-0.0514</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3425</v>
+        <v>-0.274</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1301</v>
+        <v>0.2226</v>
       </c>
       <c r="V8" t="n">
         <v>-0.7395</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. GODSPOWER JOHNSON</t>
+          <t>M. CAICEDO SANCHEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.2164</v>
+        <v>-1.1288</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2897</v>
+        <v>0.4818</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.5061</v>
+        <v>-1.6106</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.3669</v>
+        <v>0.9425</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6659</v>
+        <v>2.0135</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.0327</v>
+        <v>-1.071</v>
       </c>
       <c r="J9" t="n">
-        <v>1.6717</v>
+        <v>2.899</v>
       </c>
       <c r="K9" t="n">
-        <v>1.8797</v>
+        <v>3.1452</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.2079</v>
+        <v>-0.2462</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.0386</v>
+        <v>-1.9565</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.2138</v>
+        <v>-1.1318</v>
       </c>
       <c r="O9" t="n">
         <v>-0.8248</v>
       </c>
       <c r="P9" t="n">
-        <v>0.2175</v>
+        <v>-0.87</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.0875</v>
+        <v>-2.1751</v>
       </c>
       <c r="R9" t="n">
         <v>1.305</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.4575</v>
+        <v>-0.2665</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6850000000000001</v>
+        <v>-0.4374</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.7726</v>
+        <v>0.1709</v>
       </c>
       <c r="V9" t="n">
-        <v>0.3904</v>
+        <v>-0.9347</v>
       </c>
       <c r="W9" t="n">
-        <v>0.3904</v>
+        <v>0.1952</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S. RODRIGUEZ FEBLES</t>
+          <t>M. STILMA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.8773</v>
+        <v>-2.1823</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.6524</v>
+        <v>-2.8204</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.2249</v>
+        <v>0.6381</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.3226</v>
+        <v>-0.989</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.1465</v>
+        <v>-0.6448</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8239</v>
+        <v>-0.3442</v>
       </c>
       <c r="J10" t="n">
-        <v>0.786</v>
+        <v>-1.4336</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.6292</v>
+        <v>-0.7268</v>
       </c>
       <c r="L10" t="n">
-        <v>1.4152</v>
+        <v>-0.7068</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.1086</v>
+        <v>0.4446</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.5173</v>
+        <v>0.082</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.5913</v>
+        <v>0.3626</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.87</v>
+        <v>-0.6525</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.1751</v>
+        <v>-1.0875</v>
       </c>
       <c r="R10" t="n">
-        <v>1.305</v>
+        <v>0.435</v>
       </c>
       <c r="S10" t="n">
-        <v>0.6405</v>
+        <v>-0.5407999999999999</v>
       </c>
       <c r="T10" t="n">
-        <v>0.7367</v>
+        <v>-0.2992</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0961</v>
+        <v>-0.2415</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.3252</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.3252</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. STILMA</t>
+          <t>C. DIAZ RODRIGUEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.4173</v>
+        <v>-2.3277</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.9321</v>
+        <v>-0.6371</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5148</v>
+        <v>-1.6906</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.989</v>
+        <v>0.5813</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.6448</v>
+        <v>0.4745</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3442</v>
+        <v>0.1068</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.4336</v>
+        <v>3.113</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.7268</v>
+        <v>1.3719</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.7068</v>
+        <v>1.7412</v>
       </c>
       <c r="M11" t="n">
-        <v>0.4446</v>
+        <v>-2.5318</v>
       </c>
       <c r="N11" t="n">
-        <v>0.082</v>
+        <v>-0.8974</v>
       </c>
       <c r="O11" t="n">
-        <v>0.3626</v>
+        <v>-1.6344</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.6525</v>
+        <v>-2.8276</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.0875</v>
+        <v>-4.3501</v>
       </c>
       <c r="R11" t="n">
-        <v>0.435</v>
+        <v>1.5225</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7758</v>
+        <v>0.1139</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.411</v>
+        <v>-0.5299</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3648</v>
+        <v>0.6438</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-0.1952</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>C. DIAZ RODRIGUEZ</t>
+          <t>S. RODRIGUEZ FEBLES</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,64 +1345,64 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.5957</v>
+        <v>-2.5479</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.9976</v>
+        <v>-1.323</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.5981</v>
+        <v>-1.2249</v>
       </c>
       <c r="G12" t="n">
-        <v>0.5813</v>
+        <v>-0.3226</v>
       </c>
       <c r="H12" t="n">
-        <v>0.4745</v>
+        <v>-1.1465</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1068</v>
+        <v>0.8239</v>
       </c>
       <c r="J12" t="n">
-        <v>3.113</v>
+        <v>0.786</v>
       </c>
       <c r="K12" t="n">
-        <v>1.3719</v>
+        <v>-0.6292</v>
       </c>
       <c r="L12" t="n">
-        <v>1.7412</v>
+        <v>1.4152</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.5318</v>
+        <v>-1.1086</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.8974</v>
+        <v>-0.5173</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.6344</v>
+        <v>-0.5913</v>
       </c>
       <c r="P12" t="n">
-        <v>-2.8276</v>
+        <v>-0.87</v>
       </c>
       <c r="Q12" t="n">
-        <v>-4.3501</v>
+        <v>-2.1751</v>
       </c>
       <c r="R12" t="n">
-        <v>1.5225</v>
+        <v>1.305</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1542</v>
+        <v>-0.03</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8904</v>
+        <v>0.06610000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>0.7363</v>
+        <v>-0.0961</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.1952</v>
+        <v>-1.3252</v>
       </c>
       <c r="W12" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
         <v>-1.3252</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.2951</v>
+        <v>-2.9231</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.513</v>
+        <v>-2.2643</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.7821</v>
+        <v>-0.6588000000000001</v>
       </c>
       <c r="G13" t="n">
         <v>-3.0913</v>
@@ -1468,13 +1468,13 @@
         <v>1.305</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.4213</v>
+        <v>-0.0493</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6165</v>
+        <v>-0.3677</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1952</v>
+        <v>0.3184</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,22 +1501,22 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-6.5101</v>
+        <v>-5.825299999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.2157999999999998</v>
+        <v>0.4689000000000005</v>
       </c>
       <c r="F14" t="n">
         <v>-6.2942</v>
       </c>
       <c r="G14" t="n">
-        <v>2.625700000000001</v>
+        <v>2.625699999999999</v>
       </c>
       <c r="H14" t="n">
-        <v>2.402700000000001</v>
+        <v>2.4027</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2230000000000001</v>
+        <v>0.2229999999999996</v>
       </c>
       <c r="J14" t="n">
         <v>16.8351</v>
@@ -1531,7 +1531,7 @@
         <v>-14.2095</v>
       </c>
       <c r="N14" t="n">
-        <v>-6.9063</v>
+        <v>-6.906299999999999</v>
       </c>
       <c r="O14" t="n">
         <v>-7.303600000000001</v>
@@ -1546,16 +1546,16 @@
         <v>13.05</v>
       </c>
       <c r="S14" t="n">
-        <v>-4.590400000000001</v>
+        <v>-3.9055</v>
       </c>
       <c r="T14" t="n">
-        <v>-4.212</v>
+        <v>-3.527</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3783999999999998</v>
+        <v>-0.3786</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.1952</v>
+        <v>-0.1951999999999998</v>
       </c>
       <c r="W14" t="n">
         <v>4.561199999999999</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>R. COSIALLS BORRAS</t>
+          <t>G. PARHAM II</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.4688</v>
+        <v>6.6247</v>
       </c>
       <c r="E15" t="n">
-        <v>4.5324</v>
+        <v>5.2344</v>
       </c>
       <c r="F15" t="n">
-        <v>1.9364</v>
+        <v>1.3903</v>
       </c>
       <c r="G15" t="n">
-        <v>1.3702</v>
+        <v>3.3334</v>
       </c>
       <c r="H15" t="n">
-        <v>0.9853</v>
+        <v>2.138</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3849</v>
+        <v>1.1953</v>
       </c>
       <c r="J15" t="n">
-        <v>2.1074</v>
+        <v>5.7481</v>
       </c>
       <c r="K15" t="n">
-        <v>1.9162</v>
+        <v>3.8324</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1912</v>
+        <v>1.9157</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.7372</v>
+        <v>-2.4147</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.9308999999999999</v>
+        <v>-1.6943</v>
       </c>
       <c r="O15" t="n">
-        <v>0.1936</v>
+        <v>-0.7204</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.2175</v>
+        <v>2.8276</v>
       </c>
       <c r="Q15" t="n">
-        <v>-3.2626</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>3.0451</v>
+        <v>2.8276</v>
       </c>
       <c r="S15" t="n">
-        <v>4.5559</v>
+        <v>0.0733</v>
       </c>
       <c r="T15" t="n">
-        <v>3.7974</v>
+        <v>-0.1646</v>
       </c>
       <c r="U15" t="n">
-        <v>0.7585</v>
+        <v>0.2379</v>
       </c>
       <c r="V15" t="n">
-        <v>0.7602</v>
+        <v>0.3904</v>
       </c>
       <c r="W15" t="n">
-        <v>1.8902</v>
+        <v>-0.3491</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.13</v>
+        <v>0.7395</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>6.1957</v>
+        <v>5.9915</v>
       </c>
       <c r="E16" t="n">
-        <v>3.3421</v>
+        <v>3.2303</v>
       </c>
       <c r="F16" t="n">
-        <v>2.8537</v>
+        <v>2.7612</v>
       </c>
       <c r="G16" t="n">
         <v>2.043</v>
@@ -1702,13 +1702,13 @@
         <v>3.2626</v>
       </c>
       <c r="S16" t="n">
-        <v>1.5655</v>
+        <v>1.3612</v>
       </c>
       <c r="T16" t="n">
-        <v>0.7487</v>
+        <v>0.6369</v>
       </c>
       <c r="U16" t="n">
-        <v>0.8168</v>
+        <v>0.7243000000000001</v>
       </c>
       <c r="V16" t="n">
         <v>1.4997</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>G. PARHAM II</t>
+          <t>R. COSIALLS BORRAS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>5.4725</v>
+        <v>3.8753</v>
       </c>
       <c r="E17" t="n">
-        <v>4.4521</v>
+        <v>2.1855</v>
       </c>
       <c r="F17" t="n">
-        <v>1.0205</v>
+        <v>1.6898</v>
       </c>
       <c r="G17" t="n">
-        <v>3.3334</v>
+        <v>1.3702</v>
       </c>
       <c r="H17" t="n">
-        <v>2.138</v>
+        <v>0.9853</v>
       </c>
       <c r="I17" t="n">
-        <v>1.1953</v>
+        <v>0.3849</v>
       </c>
       <c r="J17" t="n">
-        <v>5.7481</v>
+        <v>2.1074</v>
       </c>
       <c r="K17" t="n">
-        <v>3.8324</v>
+        <v>1.9162</v>
       </c>
       <c r="L17" t="n">
-        <v>1.9157</v>
+        <v>0.1912</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.4147</v>
+        <v>-0.7372</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.6943</v>
+        <v>-0.9308999999999999</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.7204</v>
+        <v>0.1936</v>
       </c>
       <c r="P17" t="n">
-        <v>2.8276</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-3.2626</v>
       </c>
       <c r="R17" t="n">
-        <v>2.8276</v>
+        <v>3.0451</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.0789</v>
+        <v>1.9624</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.9469</v>
+        <v>1.4505</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.132</v>
+        <v>0.5119</v>
       </c>
       <c r="V17" t="n">
-        <v>0.3904</v>
+        <v>0.7602</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.3491</v>
+        <v>1.8902</v>
       </c>
       <c r="X17" t="n">
-        <v>0.7395</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.3437</v>
+        <v>3.6655</v>
       </c>
       <c r="E18" t="n">
-        <v>0.6196</v>
+        <v>1.8489</v>
       </c>
       <c r="F18" t="n">
-        <v>1.7241</v>
+        <v>1.8165</v>
       </c>
       <c r="G18" t="n">
         <v>0.8159999999999999</v>
@@ -1858,13 +1858,13 @@
         <v>3.4801</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.8649</v>
+        <v>0.457</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.4949</v>
+        <v>-0.2656</v>
       </c>
       <c r="U18" t="n">
-        <v>0.63</v>
+        <v>0.7225</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.4235</v>
+        <v>1.6971</v>
       </c>
       <c r="E19" t="n">
-        <v>2.1558</v>
+        <v>2.4911</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.7323</v>
+        <v>-0.7939000000000001</v>
       </c>
       <c r="G19" t="n">
         <v>2.476</v>
@@ -1936,13 +1936,13 @@
         <v>1.9576</v>
       </c>
       <c r="S19" t="n">
-        <v>0.3374</v>
+        <v>0.6111</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3389</v>
+        <v>-0.0036</v>
       </c>
       <c r="U19" t="n">
-        <v>0.6763</v>
+        <v>0.6147</v>
       </c>
       <c r="V19" t="n">
         <v>-2.2599</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.4379</v>
+        <v>-1.0294</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.5841</v>
+        <v>-0.3606</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.8538</v>
+        <v>-0.6688</v>
       </c>
       <c r="G20" t="n">
         <v>-1.092</v>
@@ -2014,13 +2014,13 @@
         <v>0.2175</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3682</v>
+        <v>0.0403</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.411</v>
+        <v>-0.1875</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0428</v>
+        <v>0.2277</v>
       </c>
       <c r="V20" t="n">
         <v>-0.1952</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. FAURE RIBES</t>
+          <t>D. SHELIST</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.8592</v>
+        <v>-3.1187</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.0807</v>
+        <v>-0.1638</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.7785</v>
+        <v>-2.9549</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.4017</v>
+        <v>-1.6291</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.0367</v>
+        <v>-1.0251</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.365</v>
+        <v>-0.604</v>
       </c>
       <c r="J21" t="n">
-        <v>0.3787</v>
+        <v>1.2987</v>
       </c>
       <c r="K21" t="n">
-        <v>0.8942</v>
+        <v>0.0547</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.5155999999999999</v>
+        <v>1.2439</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.7803</v>
+        <v>-2.9278</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.9308999999999999</v>
+        <v>-1.0799</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.8495</v>
+        <v>-1.8479</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.7401</v>
+        <v>-0.435</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.1751</v>
+        <v>-1.0875</v>
       </c>
       <c r="R21" t="n">
-        <v>0.435</v>
+        <v>0.6525</v>
       </c>
       <c r="S21" t="n">
-        <v>0.2825</v>
+        <v>0.07539999999999999</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4795</v>
+        <v>-0.3749</v>
       </c>
       <c r="U21" t="n">
-        <v>0.762</v>
+        <v>0.4503</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
       <c r="W21" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.1952</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>D. DUSCAK</t>
+          <t>A. FAURE RIBES</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.2646</v>
+        <v>-3.1366</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.881</v>
+        <v>-2.0807</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.3836</v>
+        <v>-1.056</v>
       </c>
       <c r="G22" t="n">
-        <v>-5.0199</v>
+        <v>-1.4017</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.6332</v>
+        <v>-0.0367</v>
       </c>
       <c r="I22" t="n">
-        <v>-3.3866</v>
+        <v>-1.365</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.4546</v>
+        <v>0.3787</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.8514</v>
+        <v>0.8942</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.6032</v>
+        <v>-0.5155999999999999</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.5652</v>
+        <v>-1.7803</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.7819</v>
+        <v>-0.9308999999999999</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.7834</v>
+        <v>-0.8495</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>-1.7401</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.0875</v>
+        <v>-2.1751</v>
       </c>
       <c r="R22" t="n">
-        <v>1.0875</v>
+        <v>0.435</v>
       </c>
       <c r="S22" t="n">
-        <v>0.6252</v>
+        <v>0.0051</v>
       </c>
       <c r="T22" t="n">
-        <v>0.5312</v>
+        <v>-0.4795</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0941</v>
+        <v>0.4846</v>
       </c>
       <c r="V22" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.13</v>
+        <v>0.1952</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>D. SHELIST</t>
+          <t>D. DUSCAK</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.4733</v>
+        <v>-3.9545</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.6108</v>
+        <v>-2.6633</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.8625</v>
+        <v>-1.2912</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.6291</v>
+        <v>-5.0199</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.0251</v>
+        <v>-1.6332</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.604</v>
+        <v>-3.3866</v>
       </c>
       <c r="J23" t="n">
-        <v>1.2987</v>
+        <v>-2.4546</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0547</v>
+        <v>-0.8514</v>
       </c>
       <c r="L23" t="n">
-        <v>1.2439</v>
+        <v>-1.6032</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.9278</v>
+        <v>-2.5652</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.0799</v>
+        <v>-0.7819</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.8479</v>
+        <v>-1.7834</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.435</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R23" t="n">
-        <v>0.6525</v>
+        <v>1.0875</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.2792</v>
+        <v>-0.0646</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.822</v>
+        <v>-0.2511</v>
       </c>
       <c r="U23" t="n">
-        <v>0.5427999999999999</v>
+        <v>0.1866</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.13</v>
+        <v>1.13</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.3589</v>
+        <v>-4.1046</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.651</v>
+        <v>-3.4275</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.7079</v>
+        <v>-0.6771</v>
       </c>
       <c r="G24" t="n">
         <v>-3.5214</v>
@@ -2326,13 +2326,13 @@
         <v>0.435</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.1849</v>
+        <v>0.0694</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.2055</v>
+        <v>0.018</v>
       </c>
       <c r="U24" t="n">
-        <v>0.0205</v>
+        <v>0.0514</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,28 +2359,28 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>6.510299999999997</v>
+        <v>6.510300000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>6.2944</v>
+        <v>6.2943</v>
       </c>
       <c r="F25" t="n">
-        <v>0.2161000000000004</v>
+        <v>0.2159000000000006</v>
       </c>
       <c r="G25" t="n">
-        <v>-2.6255</v>
+        <v>-2.625500000000001</v>
       </c>
       <c r="H25" t="n">
         <v>-2.4026</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.2228000000000003</v>
+        <v>-0.2227999999999999</v>
       </c>
       <c r="J25" t="n">
         <v>14.2097</v>
       </c>
       <c r="K25" t="n">
-        <v>6.906099999999999</v>
+        <v>6.9061</v>
       </c>
       <c r="L25" t="n">
         <v>7.3034</v>
@@ -2395,7 +2395,7 @@
         <v>-7.5265</v>
       </c>
       <c r="P25" t="n">
-        <v>4.3501</v>
+        <v>4.350099999999999</v>
       </c>
       <c r="Q25" t="n">
         <v>-13.0503</v>
@@ -2404,13 +2404,13 @@
         <v>17.4005</v>
       </c>
       <c r="S25" t="n">
-        <v>4.5904</v>
+        <v>4.590599999999999</v>
       </c>
       <c r="T25" t="n">
-        <v>0.3786000000000004</v>
+        <v>0.3785999999999999</v>
       </c>
       <c r="U25" t="n">
-        <v>4.211799999999999</v>
+        <v>4.2119</v>
       </c>
       <c r="V25" t="n">
         <v>0.1952000000000003</v>
